--- a/results/0916-all/冀鲁豫低洼平原农业区/tech_selected_summary.xlsx
+++ b/results/0916-all/冀鲁豫低洼平原农业区/tech_selected_summary.xlsx
@@ -409,220 +409,220 @@
     <t>长垣县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -715,7 +715,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 70955302.87</t>
+    <t>70955302.87</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -784,13 +784,13 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 212465649.67</t>
+    <t>212465649.67</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 44062878.45</t>
+    <t>44062878.45</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -808,7 +808,7 @@
     <t>4R(Right type)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 105572133.73</t>
+    <t>105572133.73</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -832,7 +832,7 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 265049088.65</t>
+    <t>265049088.65</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -886,22 +886,22 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 444630284.27</t>
-  </si>
-  <si>
-    <t>总经济成本: 271181228.92</t>
+    <t>444630284.27</t>
+  </si>
+  <si>
+    <t>271181228.92</t>
   </si>
   <si>
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 145445329.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 116367312.43</t>
+    <t>145445329.40</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>116367312.43</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
@@ -910,28 +910,28 @@
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 292768155.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 64894210.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 162892757.40</t>
+    <t>292768155.95</t>
+  </si>
+  <si>
+    <t>64894210.32</t>
+  </si>
+  <si>
+    <t>162892757.40</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 268896813.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 99201046.94</t>
+    <t>268896813.10</t>
+  </si>
+  <si>
+    <t>99201046.94</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 408205480.33</t>
+    <t>408205480.33</t>
   </si>
   <si>
     <t>Chemical amendments_pig</t>
@@ -943,10 +943,10 @@
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 728041852.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 206407631.62</t>
+    <t>728041852.79</t>
+  </si>
+  <si>
+    <t>206407631.62</t>
   </si>
   <si>
     <t>Oil_dairy</t>
@@ -955,25 +955,25 @@
     <t>compost（mid）30%-70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 139065704.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 265481832.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 687359239.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 171421455.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 324224499.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 316709240.55</t>
-  </si>
-  <si>
-    <t>总经济成本: 47700866.64</t>
+    <t>139065704.05</t>
+  </si>
+  <si>
+    <t>265481832.26</t>
+  </si>
+  <si>
+    <t>687359239.73</t>
+  </si>
+  <si>
+    <t>171421455.40</t>
+  </si>
+  <si>
+    <t>324224499.38</t>
+  </si>
+  <si>
+    <t>316709240.55</t>
+  </si>
+  <si>
+    <t>47700866.64</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
@@ -982,25 +982,25 @@
     <t>incorporation_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 150566895.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 269153532.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 303215349.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 342563957.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 72252753.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 147604963.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 68765264.54</t>
+    <t>150566895.44</t>
+  </si>
+  <si>
+    <t>269153532.97</t>
+  </si>
+  <si>
+    <t>303215349.99</t>
+  </si>
+  <si>
+    <t>342563957.32</t>
+  </si>
+  <si>
+    <t>72252753.92</t>
+  </si>
+  <si>
+    <t>147604963.04</t>
+  </si>
+  <si>
+    <t>68765264.54</t>
   </si>
   <si>
     <t>EEF(DI)_wheat</t>
@@ -1009,7 +1009,7 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 75477263.18</t>
+    <t>75477263.18</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -1018,49 +1018,49 @@
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 105555407.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 188390730.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 54839702.60</t>
+    <t>105555407.65</t>
+  </si>
+  <si>
+    <t>188390730.93</t>
+  </si>
+  <si>
+    <t>54839702.60</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 1059394428.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 67608589.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 301710651.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 127865504.74</t>
+    <t>1059394428.85</t>
+  </si>
+  <si>
+    <t>67608589.78</t>
+  </si>
+  <si>
+    <t>301710651.64</t>
+  </si>
+  <si>
+    <t>127865504.74</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 329610374.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 243063039.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 226857670.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 318871113.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 164398690.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 57859036.20</t>
+    <t>329610374.59</t>
+  </si>
+  <si>
+    <t>243063039.13</t>
+  </si>
+  <si>
+    <t>226857670.07</t>
+  </si>
+  <si>
+    <t>318871113.71</t>
+  </si>
+  <si>
+    <t>164398690.33</t>
+  </si>
+  <si>
+    <t>57859036.20</t>
   </si>
   <si>
     <t>Optimized aeration_pig</t>
@@ -1069,31 +1069,31 @@
     <t>residue rerention_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 530888262.80</t>
+    <t>530888262.80</t>
   </si>
   <si>
     <t>compost（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 31879787.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 143988613.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 400983085.87</t>
+    <t>31879787.13</t>
+  </si>
+  <si>
+    <t>143988613.65</t>
+  </si>
+  <si>
+    <t>400983085.87</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 490428914.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 178363652.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 368128378.32</t>
+    <t>490428914.67</t>
+  </si>
+  <si>
+    <t>178363652.87</t>
+  </si>
+  <si>
+    <t>368128378.32</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -1105,16 +1105,16 @@
     <t>Cover_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 824794889.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 578345.32</t>
+    <t>824794889.26</t>
+  </si>
+  <si>
+    <t>578345.32</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 151901315.75</t>
+    <t>151901315.75</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_wheat</t>
@@ -1123,181 +1123,181 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 175376172.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 831649317.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 114890570.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 1148638506.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 239593477.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 344096224.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 88626720.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 445898514.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 176509308.57</t>
+    <t>175376172.24</t>
+  </si>
+  <si>
+    <t>831649317.31</t>
+  </si>
+  <si>
+    <t>114890570.22</t>
+  </si>
+  <si>
+    <t>1148638506.41</t>
+  </si>
+  <si>
+    <t>239593477.22</t>
+  </si>
+  <si>
+    <t>344096224.28</t>
+  </si>
+  <si>
+    <t>88626720.12</t>
+  </si>
+  <si>
+    <t>445898514.02</t>
+  </si>
+  <si>
+    <t>176509308.57</t>
   </si>
   <si>
     <t>Acidification_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 826755167.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 699934146.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 144064396.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 480788570.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 62828989.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 142610196.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 174195515.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 391481233.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 142440652.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 123442720.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 330251858.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 218887193.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 377559320.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 356883183.77</t>
+    <t>826755167.80</t>
+  </si>
+  <si>
+    <t>699934146.20</t>
+  </si>
+  <si>
+    <t>144064396.00</t>
+  </si>
+  <si>
+    <t>480788570.54</t>
+  </si>
+  <si>
+    <t>62828989.01</t>
+  </si>
+  <si>
+    <t>142610196.47</t>
+  </si>
+  <si>
+    <t>174195515.95</t>
+  </si>
+  <si>
+    <t>391481233.78</t>
+  </si>
+  <si>
+    <t>142440652.52</t>
+  </si>
+  <si>
+    <t>123442720.26</t>
+  </si>
+  <si>
+    <t>330251858.92</t>
+  </si>
+  <si>
+    <t>218887193.84</t>
+  </si>
+  <si>
+    <t>377559320.51</t>
+  </si>
+  <si>
+    <t>356883183.77</t>
   </si>
   <si>
     <t>Acidification_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 167656885.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 127177984.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 97394528.01</t>
+    <t>167656885.38</t>
+  </si>
+  <si>
+    <t>127177984.89</t>
+  </si>
+  <si>
+    <t>97394528.01</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 452318628.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 291515629.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 124428293.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 351017776.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 128626583.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 80316602.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 94448131.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 384989303.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 223498266.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 58379004.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 182007776.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 218529491.60</t>
+    <t>452318628.70</t>
+  </si>
+  <si>
+    <t>291515629.43</t>
+  </si>
+  <si>
+    <t>124428293.54</t>
+  </si>
+  <si>
+    <t>351017776.23</t>
+  </si>
+  <si>
+    <t>128626583.10</t>
+  </si>
+  <si>
+    <t>80316602.07</t>
+  </si>
+  <si>
+    <t>94448131.35</t>
+  </si>
+  <si>
+    <t>384989303.98</t>
+  </si>
+  <si>
+    <t>223498266.09</t>
+  </si>
+  <si>
+    <t>58379004.30</t>
+  </si>
+  <si>
+    <t>182007776.49</t>
+  </si>
+  <si>
+    <t>218529491.60</t>
   </si>
   <si>
     <t>nitrification inhibitor_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 84133461.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 17794581.68</t>
+    <t>84133461.54</t>
+  </si>
+  <si>
+    <t>17794581.68</t>
   </si>
   <si>
     <t>4R(Right place)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 346027914.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 78742987.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 886446275.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 575934202.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 256048425.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 503817552.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 523104508.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 99730154.67</t>
+    <t>346027914.82</t>
+  </si>
+  <si>
+    <t>78742987.87</t>
+  </si>
+  <si>
+    <t>886446275.85</t>
+  </si>
+  <si>
+    <t>575934202.50</t>
+  </si>
+  <si>
+    <t>256048425.39</t>
+  </si>
+  <si>
+    <t>503817552.35</t>
+  </si>
+  <si>
+    <t>523104508.93</t>
+  </si>
+  <si>
+    <t>99730154.67</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 213018131.45</t>
+    <t>213018131.45</t>
   </si>
   <si>
     <t>Bioflilter_pig</t>
   </si>
   <si>
-    <t>总经济成本: 909579080.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 142472602.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 403045288.49</t>
+    <t>909579080.86</t>
+  </si>
+  <si>
+    <t>142472602.60</t>
+  </si>
+  <si>
+    <t>403045288.49</t>
   </si>
 </sst>
 </file>
